--- a/NV_DEMO/Assets/StreamingAssets/Story/1-2.xlsx
+++ b/NV_DEMO/Assets/StreamingAssets/Story/1-2.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="195">
   <si>
     <t>中文姓名</t>
   </si>
@@ -67,13 +67,25 @@
     <t>Character2</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>Toid</t>
+  </si>
+  <si>
+    <t>Char1Anim</t>
+  </si>
+  <si>
+    <t>Char2Anim</t>
+  </si>
+  <si>
     <t>D城的傍晚一如既往地温吞，我们的影子在斑驳的墙面上拉得很长 。</t>
   </si>
   <si>
     <t>street_Dusk</t>
   </si>
   <si>
-    <t>Happiness</t>
+    <t>Happiness Day</t>
   </si>
   <si>
     <t>张杨</t>
@@ -94,7 +106,7 @@
     <t>张杨一边踢着路上的小石子，一边神神秘秘地凑过来。</t>
   </si>
   <si>
-    <t>上个星期，那地方彻底断电封锁了，听说是因为地基沉降太厉害，整栋楼都开始歪了，成了危楼。</t>
+    <t>「上个星期，那地方彻底断电封锁了，听说是因为地基沉降太厉害，整栋楼都开始歪了，成了危楼。」</t>
   </si>
   <si>
     <t>我看着远处纺织厂的方向，那一带确实已经很久没有灯火了。</t>
@@ -109,21 +121,27 @@
     <t>zhangYang_excited</t>
   </si>
   <si>
+    <t>JUMP</t>
+  </si>
+  <si>
     <t>「越是这种地方，越有意思。我听那些搬出来的老住户说，那栋楼的顶层天台视线特别好，能看清大半个D城的夜景 。而且，里面肯定还留着不少没带走的旧东西，简直就是个时光胶囊。」</t>
   </si>
   <si>
+    <t>zhangYang_smile</t>
+  </si>
+  <si>
     <t>「你就不怕被保安抓到？」</t>
   </si>
   <si>
     <t>「哪来的保安啊，这破地方谁管？」</t>
   </si>
   <si>
+    <t>「而且我告诉你一个真正的都市传说：听说那顶楼天台有个“空间裂缝”，站在那儿大喊一声，城外世界就能听到你的声音。」</t>
+  </si>
+  <si>
     <t>zhangYang_serious</t>
   </si>
   <si>
-    <t>「而且我告诉你一个真正的都市传说：听说那顶楼天台有个“空间裂缝”，站在那儿大喊一声，城外世界就能听到你的声音。」</t>
-  </si>
-  <si>
     <t>「真的？」</t>
   </si>
   <si>
@@ -142,7 +160,7 @@
     <t>「当然不是！正事当然要等到上桌了再谈。」</t>
   </si>
   <si>
-    <t>zhangYang_smile</t>
+    <t>NO</t>
   </si>
   <si>
     <t>「...你还搞的怪神秘的。」</t>
@@ -192,7 +210,7 @@
     <t>「还是老样子，说那边忙，过年才回来。」</t>
   </si>
   <si>
-    <t>「我爸妈也一样。」张杨笑了一下，语气听不出情绪，「一年到头见不着人。」</t>
+    <t>「我爸妈也一样。」张杨的语气听不出情绪，「一年到头见不着人。」</t>
   </si>
   <si>
     <t>zhangYang_upset</t>
@@ -290,30 +308,33 @@
     <t>bbq1</t>
   </si>
   <si>
-    <t>Funny</t>
-  </si>
-  <si>
     <t>周五下课后的炸串店正是生意最红火的时候，推门进去，一股夹杂着辣椒、孜然和滚烫油脂香味的热浪扑面而来 。店内空间并不大，天花板上悬挂着的旧吊扇正嗡嗡地转动，却驱不散空气中那股黏稠的油烟气。</t>
   </si>
   <si>
     <t>「哎，等下，那边的位置快空了。」张杨眼尖，在嘈杂的人群中迅速锁定了靠窗的一个角落。</t>
   </si>
   <si>
+    <t>Funny Tiff</t>
+  </si>
+  <si>
     <t>此时，几个穿着初中部校服的男生正一边擦嘴一边起身离开。张杨眼疾手快地跨步过去，并从口袋里掏出一包纸巾，仔细地擦拭着那张残留着几滴红油的深色木桌。周围的学生们都在大快朵颐、高声说笑，而他那副专注擦桌子、生怕弄脏校服袖口的模样，倒显得与这充满烟火气的环境有些格格不入。</t>
   </si>
   <si>
     <t>「坐吧，这儿干净点。」</t>
   </si>
   <si>
-    <t>「老板娘，这边点单！」</t>
-  </si>
-  <si>
-    <t>老板娘应了一声，从油锅后面探出头来，张杨已经把一张钞票“啪”地一声压在桌上，动作利索，像是生怕慢一秒就显得不够痛快。</t>
+    <t>「老板，这边点单！」</t>
+  </si>
+  <si>
+    <t>老板应了一声，从油锅后面探出头来，张杨已经把一张钞票“啪”地一声压在桌上，动作利索，像是生怕慢一秒就显得不够痛快。</t>
   </si>
   <si>
     <t>「五串炸鸡排，五串开花肠，五串鸡皮，翅根、鸡柳各来两份，再来两瓶冰汽水。」</t>
   </si>
   <si>
+    <t>zhangYang_curious</t>
+  </si>
+  <si>
     <t>「什么情况，你在哪发财了？」</t>
   </si>
   <si>
@@ -347,7 +368,10 @@
     <t>...这小子十分有十二分的不对劲。</t>
   </si>
   <si>
-    <t>「老王今天对唐梅发火了。」他捏着那块纸巾的手停在半空，像是突然意识到自己说漏了什么，又若无其事地继续折，边角却被他压得发白。</t>
+    <t>「老王今天对唐梅发火了。」</t>
+  </si>
+  <si>
+    <t>他捏着那块纸巾的手停在半空，像是突然意识到自己说漏了什么，又若无其事地继续折，边角却被他压得发白。</t>
   </si>
   <si>
     <t>「他对他们班班长发火？」</t>
@@ -356,7 +380,7 @@
     <t>在我印象里，唐梅一直都是认真学习的学霸模样，老王连当了他们班两年的班长都要训斥吗？</t>
   </si>
   <si>
-    <t>「就是她。」</t>
+    <t>「对，就是她。」</t>
   </si>
   <si>
     <t>空气好像安静了一瞬。</t>
@@ -377,7 +401,13 @@
     <t>「随便问问。」</t>
   </si>
   <si>
-    <t>他说得很快，「假设，假设。」</t>
+    <t>zhangyang_astonished</t>
+  </si>
+  <si>
+    <t>他说得很快。</t>
+  </si>
+  <si>
+    <t>「假设，假设。」</t>
   </si>
   <si>
     <t>「假设啊——」</t>
@@ -422,6 +452,9 @@
     <t>「小点声！」他压低嗓音，耳根却红得要命，「你想让全店都听见吗？」</t>
   </si>
   <si>
+    <t>zhangYang_angry</t>
+  </si>
+  <si>
     <t>我愣了一秒，随即反应过来，心跳一下子快了。</t>
   </si>
   <si>
@@ -431,6 +464,9 @@
     <t>「闭嘴！」他几乎是咬着牙说的，「你小点声！」</t>
   </si>
   <si>
+    <t>SHOCK</t>
+  </si>
+  <si>
     <t>我看着他这副前所未有的样子，忽然有点想笑，又有点不敢笑。</t>
   </si>
   <si>
@@ -440,7 +476,7 @@
     <t>他沉默了几秒，终于认命似的吐出一句：</t>
   </si>
   <si>
-    <t>「……嗯。」</t>
+    <t>「...嗯。」</t>
   </si>
   <si>
     <t>「喔~~~~」</t>
@@ -458,147 +494,184 @@
     <t>「我是认真的！」</t>
   </si>
   <si>
-    <t>zhangYang_angry</t>
-  </si>
-  <si>
     <t>「这事儿我谁都没告诉，你是第一个知道的。」</t>
   </si>
   <si>
     <t>「这我倒不惊讶，只是......你怎么看上她了？」</t>
   </si>
   <si>
+    <t>「......」</t>
+  </si>
+  <si>
+    <t>「喂，你不说话，我可没法帮你。」</t>
+  </si>
+  <si>
+    <t>「其实...我也不是很清楚，可能是送数学作业的时候总能看见她吧。」</t>
+  </si>
+  <si>
+    <t>zhangyang_curious</t>
+  </si>
+  <si>
+    <t>「每次在办公室礼貌地跟给每个老师打招呼，做事情明明很认真但感觉又有些笨手笨脚的...」</t>
+  </si>
+  <si>
+    <t>「一开始我没怎么在意，但不知道什么时候竟然开始期待每天下早自习能跟她一起去送作业了...」</t>
+  </si>
+  <si>
+    <t>「看不见她，心里也会空落落的。」</t>
+  </si>
+  <si>
+    <t>看得出来，他没有在开玩笑。</t>
+  </si>
+  <si>
+    <t>「所以......我是喜欢她对吗？」</t>
+  </si>
+  <si>
+    <t>「我想是的。」</t>
+  </si>
+  <si>
+    <t>「那我该怎么做？」</t>
+  </si>
+  <si>
+    <t>是啊，该怎么做呢？张杨和我在学校里都没什么朋友，就凭我们俩和唐梅搭上话都很难，更别提处好关系了。</t>
+  </si>
+  <si>
+    <t>正好此时，老板端着两大盘香气四溢的炸串搁在了桌上。我的鸡皮烤得金黄微焦，滋滋冒着热气，但我已经没有了什么胃口，好兄弟有喜欢的人这事固然令我兴奋，但对象——在D城这种充满烟火气的地方，却活得像一株清冷孤傲的空谷幽兰般的女生，我实在没办法想象唐梅会有对一个男生倾心的可能。</t>
+  </si>
+  <si>
+    <t>bbq2</t>
+  </si>
+  <si>
+    <t>「你俩现在熟吗？」</t>
+  </si>
+  <si>
+    <t>「仅仅是认识的程度吧，在走廊碰见，她要么是在看书，要么是在送作业，要么就是在想事情，我感觉我就算在她面前摔个跟头，她也只会绕着走。」</t>
+  </si>
+  <si>
+    <t>其实也不难预见。唐梅是那种独来独往惯了的女生，每天准时出现在教室、食堂、图书馆，路径精准得像程序设定好的。她对所有男生都保持着那种礼貌的距离感，像是一道无形的屏障，把所有的躁动都隔绝在外。</t>
+  </si>
+  <si>
+    <t>「她好像对所有男生都这样。」</t>
+  </si>
+  <si>
+    <t>「很难办，不是吗？」</t>
+  </si>
+  <si>
+    <t>「不试试怎么知道呢，你们现在需要一个契机认识一下彼此。」</t>
+  </si>
+  <si>
+    <t>「我明白，但我对她什么都不了解，总不能硬着头皮上去搭讪吧？」</t>
+  </si>
+  <si>
+    <t>choice</t>
+  </si>
+  <si>
+    <t>打直球！直球永远是对的！| 时机还不成熟。</t>
+  </si>
+  <si>
+    <t>109|112</t>
+  </si>
+  <si>
+    <t>「可我俩还不熟啊。」</t>
+  </si>
+  <si>
+    <t>「...她会喜欢这样主动的男生吗？」</t>
+  </si>
+  <si>
+    <t>...还是不逗他了。</t>
+  </si>
+  <si>
+    <t>「当然不行，我想她一定会很讨厌刻意的显摆和那种带着目的性的搭讪，你得先从日常小事铺垫起，让她在不经意间留下对你好印象。」</t>
+  </si>
+  <si>
+    <t>他若有所思，但随即又露出苦恼的表情。</t>
+  </si>
+  <si>
+    <t>「她根本就不会注意我！」</t>
+  </si>
+  <si>
+    <t>「下周，篮球班赛就要开始了，这可是全校围观的项目，唐梅作为班长，就算再不喜欢凑热闹，肯定也得去当志愿者。」</t>
+  </si>
+  <si>
+    <t>「对哦，如果我能在球赛上大杀四方......」</t>
+  </si>
+  <si>
+    <t>......人家都不一定会看你打球好吗</t>
+  </si>
+  <si>
+    <t>「不过你真能大杀四方倒也不赖。」</t>
+  </si>
+  <si>
+    <t>「那你是什么意思？」</t>
+  </si>
+  <si>
+    <t>「我只是说你能有和她说话的正当理由了。」</t>
+  </si>
+  <si>
+    <t>「跟她要瓶水，要个毛巾什么的。」</t>
+  </si>
+  <si>
+    <t>张杨愣了愣。</t>
+  </si>
+  <si>
+    <t>「这也太普通了吧？」</t>
+  </si>
+  <si>
+    <t>「那你还想怎么样嘛，要不然让唐梅赛后帮你捶捶腿？」</t>
+  </si>
+  <si>
+    <t>「也不是不行。」</t>
+  </si>
+  <si>
+    <t>「要不这样，你赛后留下来帮她一起打扫球场吧。」</t>
+  </si>
+  <si>
+    <t>「打扫球场？」</t>
+  </si>
+  <si>
+    <t>「对，你想啊，那么多围观的同学，赛后球场一定很乱吧，更别提他们志愿者还要把各种东西搬回器材室了。」</t>
+  </si>
+  <si>
+    <t>「反正到时候你就盯着唐梅帮，在那样的环境下，她总得说声谢谢吧。」</t>
+  </si>
+  <si>
+    <t>「这样做会不会太刻意了点？」</t>
+  </si>
+  <si>
+    <t>「那你就到处帮帮忙呗，总之，只是为了在她心里留下一个对你还不错的印象——」</t>
+  </si>
+  <si>
+    <t>「你刚打完比赛还愿意留下帮忙，她应该会看在眼里吧？」</t>
+  </si>
+  <si>
+    <t>「我明白了，谢谢你，[Name]。」</t>
+  </si>
+  <si>
+    <t>「你跟我客气啥，况且我又不白给你出主意。」</t>
+  </si>
+  <si>
+    <t>结完账，我和张杨在老街的路口挥手告别。</t>
+  </si>
+  <si>
+    <t>喧嚣声随着他的背影一同消失在街角，原本被油烟和笑闹充斥的空气，瞬间被夜晚略带潮湿的凉风冲散。我独自穿过那几条曲折的石板小巷，路灯将我的影子拉长、缩短，又再次拉长。</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>......</t>
   </si>
   <si>
-    <t>「喂，你不说话，我可没法帮你。」</t>
-  </si>
-  <si>
-    <t>「其实......我也不是很清楚，可能是送数学作业的时候总能看见她吧，每次在办公室礼貌地跟给每个老师打招呼，做事情明明很认真但感觉又有些笨手笨脚的......一开始我没怎么在意，但不知道什么时候竟然开始期待每天下早自习能跟她一起去送作业了，看不见她，心里也会空落落的。」</t>
-  </si>
-  <si>
-    <t>看得出来，他没有在开玩笑。</t>
-  </si>
-  <si>
-    <t>「所以......我是喜欢她对吗？」</t>
-  </si>
-  <si>
-    <t>「我想是的。」</t>
-  </si>
-  <si>
-    <t>「那我该怎么做？」</t>
-  </si>
-  <si>
-    <t>是啊，该怎么做呢？张杨和我在学校里都没什么朋友，就凭我们俩和唐梅搭上话都很难，更别提处好关系了。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>正好此时，老板娘端着两大盘香气四溢的炸串搁在了桌上。我的鸡皮烤得金黄微焦，滋滋冒着热气</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，但我已经没有了什么胃口，好兄弟有喜欢的人这事固然令我兴奋，但对象——</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>在D城这种充满烟火气的地方，却活得像一株清冷孤傲的空谷幽兰般的女生，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我实在没办法想象唐梅会有对一个男生倾心的可能。</t>
-    </r>
-  </si>
-  <si>
-    <t>「你俩现在熟吗？」</t>
-  </si>
-  <si>
-    <t>「仅仅是认识的程度吧，在走廊碰见，她要么是在看书，要么是在送作业，要么就是在想事情，我感觉我就算在她面前摔个跟头，她也只会绕着走。」</t>
-  </si>
-  <si>
-    <t>其实也不难预见。唐梅是那种独来独往惯了的女生，每天准时出现在教室、食堂、图书馆，路径精准得像程序设定好的。她对所有男生都保持着那种礼貌却疏离的距离感，像是一道无形的屏障，把所有的躁动都隔绝在外。</t>
-  </si>
-  <si>
-    <t>「她好像对所有男生都这样。」</t>
-  </si>
-  <si>
-    <t>「很难办，不是吗？」</t>
-  </si>
-  <si>
-    <t>「不试试怎么知道呢，你们现在需要一个契机认识一下彼此。」</t>
-  </si>
-  <si>
-    <t>「我明白，但我对她什么都不了解，总不能硬着头皮上去搭讪吧？」</t>
-  </si>
-  <si>
-    <t>「当然不是，我想她一定会很讨厌刻意的显摆和那种带着目的性的搭讪，我觉得你得先从日常小事铺垫起，让她在不经意间留下对你好的印象。」</t>
-  </si>
-  <si>
-    <t>张杨若有所思，但随即又露出苦恼的表情。</t>
-  </si>
-  <si>
-    <t>「她根本就不会注意我！」</t>
-  </si>
-  <si>
-    <t>「下周，篮球班赛就要开始了，这可是全校围观的项目，唐梅作为班长，就算再不喜欢凑热闹，肯定也得去当志愿者。」</t>
-  </si>
-  <si>
-    <t>「哦对，如果我能在球赛上大杀四方......」</t>
-  </si>
-  <si>
-    <t>「重点不是要你在场上投进几个球，而是你有了正当和唐梅说话的机会——安安静静地走到角落，去找那个志愿者，很有礼貌地、甚至带着点疲态地问她借一件最普通的东西，比如一张记分表，一瓶水，或者赛后帮她一起打扫一下现场。」</t>
-  </si>
-  <si>
-    <t>张杨愣了愣。</t>
-  </si>
-  <si>
-    <t>「这也太普通了吧？」</t>
-  </si>
-  <si>
-    <t>「就是因为普通才真实。在那样的时刻，所有人都把你们当偶像，你却偏偏注意到她这个正在角落默默干活的志愿者，过去帮她拎一下那个重得要命的矿泉水箱，或者帮她把被风吹散的表格捡起来。不需要长篇大论，只需要一个眼神，一次伸手。你想想，在那样的环境下，你帮她解决了麻烦，她总得说声谢谢吧？」</t>
-  </si>
-  <si>
-    <t>「我明白了，谢谢你，[Name]。」</t>
-  </si>
-  <si>
-    <t>「客气啥，况且我又不白给你出主意。」</t>
-  </si>
-  <si>
-    <t>结完账，我和张杨在老街的路口挥手告别。</t>
-  </si>
-  <si>
-    <t>喧嚣声随着他的背影一同消失在街角，原本被油烟和笑闹充斥的空气，瞬间被夜晚略带潮湿的凉风冲散。我独自穿过那几条曲折的石板小巷，路灯将我的影子拉长、缩短，又再次拉长。</t>
-  </si>
-  <si>
-    <t>...</t>
-  </si>
-  <si>
-    <t>None</t>
+    <t>homeoutside_Night</t>
   </si>
   <si>
     <t>到家了，好累...</t>
   </si>
   <si>
-    <t>livingroom_Night</t>
+    <t>livingroom_Night2</t>
   </si>
   <si>
     <t>推开门，屋子里黑漆漆的。</t>
@@ -953,13 +1026,13 @@
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1758,11 +1831,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P135"/>
+  <dimension ref="A1:P157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="76.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="2" max="2" width="45.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="9" max="9" width="20.375" customWidth="1"/>
@@ -1806,120 +1879,163 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" ht="27" spans="1:16">
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
       <c r="N2" s="2"/>
       <c r="P2" s="2"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" ht="25.5" spans="1:16">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
       </c>
       <c r="N3" s="2"/>
       <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="B5" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>24</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="25.5" spans="1:16">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="I6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="25.5" spans="1:16">
       <c r="B7" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>26</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="25.5" spans="1:16">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="M9">
+        <v>8</v>
+      </c>
+      <c r="O9" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="61" customHeight="1" spans="1:16">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>32</v>
+      </c>
+      <c r="M10">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
         <v>29</v>
@@ -1927,603 +2043,882 @@
       <c r="I12" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" ht="25.5" spans="1:16">
+      <c r="M12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" ht="38.25" spans="1:16">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I13" t="s">
-        <v>29</v>
+        <v>36</v>
+      </c>
+      <c r="M13">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
+      </c>
+      <c r="M14">
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>39</v>
+      </c>
+      <c r="M15">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18">
+        <v>17</v>
+      </c>
+      <c r="O18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" ht="52.5" spans="1:15">
+      <c r="B20" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" t="s">
+        <v>47</v>
+      </c>
+      <c r="M20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" ht="25.5" spans="1:15">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="38.25" spans="1:15">
+      <c r="B22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" ht="25.5" spans="1:15">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" t="s">
+        <v>52</v>
+      </c>
+      <c r="M24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" ht="25.5" spans="1:15">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" t="s">
+        <v>29</v>
+      </c>
+      <c r="M25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" ht="114.75" spans="1:15">
+      <c r="B26" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="B27" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="B28" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" t="s">
+        <v>29</v>
+      </c>
+      <c r="M29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" ht="25.5" spans="1:15">
+      <c r="B30" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" t="s">
+        <v>59</v>
+      </c>
+      <c r="M30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" ht="51" spans="1:15">
+      <c r="B31" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="M31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" ht="25.5" spans="1:15">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" t="s">
+        <v>62</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" ht="76.5" spans="1:13">
+      <c r="B33" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" t="s">
+        <v>29</v>
+      </c>
+      <c r="M35">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="4" t="s">
+    <row r="36" ht="38.25" spans="1:13">
+      <c r="B36" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="M36">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="4" t="s">
+    <row r="37" ht="25.5" spans="1:13">
+      <c r="A37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="I37" t="s">
+        <v>68</v>
+      </c>
+      <c r="M37">
         <v>36</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="M38">
         <v>37</v>
       </c>
-      <c r="I18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" t="s">
+        <v>39</v>
+      </c>
+      <c r="I39" t="s">
+        <v>39</v>
+      </c>
+      <c r="M39">
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="39.75" spans="1:9">
-      <c r="B20" s="6" t="s">
+    <row r="40" ht="38.25" spans="1:13">
+      <c r="B40" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M40">
         <v>39</v>
       </c>
-      <c r="E20" t="s">
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M41">
         <v>40</v>
       </c>
-      <c r="F20" t="s">
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="4" t="s">
+    <row r="43" spans="1:13">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M43">
         <v>42</v>
       </c>
-      <c r="C21" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" ht="25.5" spans="1:9">
-      <c r="B22" s="4" t="s">
+    </row>
+    <row r="44" ht="27" spans="1:13">
+      <c r="A44" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" t="s">
+        <v>36</v>
+      </c>
+      <c r="I44" t="s">
+        <v>36</v>
+      </c>
+      <c r="M44">
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="4" t="s">
+    <row r="45" spans="1:13">
+      <c r="A45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M45">
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="4" t="s">
+    <row r="46" ht="27" spans="1:13">
+      <c r="A46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" t="s">
+        <v>39</v>
+      </c>
+      <c r="I46" t="s">
+        <v>39</v>
+      </c>
+      <c r="M46">
         <v>45</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M47">
         <v>46</v>
       </c>
-      <c r="I24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="4" t="s">
+    </row>
+    <row r="48" spans="1:13">
+      <c r="B48" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M48">
         <v>47</v>
       </c>
-      <c r="C25" t="s">
-        <v>25</v>
-      </c>
-      <c r="I25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" ht="63.75" spans="1:9">
-      <c r="B26" s="6" t="s">
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" t="s">
+        <v>39</v>
+      </c>
+      <c r="I49" t="s">
+        <v>39</v>
+      </c>
+      <c r="M49">
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
-      <c r="B27" s="6" t="s">
+    <row r="50" ht="40.5" spans="1:13">
+      <c r="B50" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M50">
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
-      <c r="B28" s="6" t="s">
+    <row r="51" spans="1:13">
+      <c r="A51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="M51">
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="4" t="s">
+    <row r="52" ht="27" spans="1:13">
+      <c r="B52" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M52">
         <v>51</v>
       </c>
-      <c r="C29" t="s">
-        <v>25</v>
-      </c>
-      <c r="I29" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="B30" s="6" t="s">
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" t="s">
+        <v>39</v>
+      </c>
+      <c r="I53" t="s">
+        <v>39</v>
+      </c>
+      <c r="M53">
         <v>52</v>
       </c>
-      <c r="E30" t="s">
+    </row>
+    <row r="54" spans="1:13">
+      <c r="B54" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M54">
         <v>53</v>
       </c>
-      <c r="F30" t="s">
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" t="s">
+        <v>52</v>
+      </c>
+      <c r="I55" t="s">
+        <v>52</v>
+      </c>
+      <c r="M55">
         <v>54</v>
       </c>
     </row>
-    <row r="31" ht="38.25" spans="1:9">
-      <c r="B31" s="5" t="s">
+    <row r="56" ht="27" spans="1:13">
+      <c r="A56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C56" t="s">
+        <v>52</v>
+      </c>
+      <c r="I56" t="s">
+        <v>52</v>
+      </c>
+      <c r="M56">
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" s="4" t="s">
+    <row r="57" spans="1:13">
+      <c r="B57" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M57">
         <v>56</v>
       </c>
-      <c r="C32" t="s">
-        <v>17</v>
-      </c>
-      <c r="I32" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" ht="51" spans="1:9">
-      <c r="B33" s="6" t="s">
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M58">
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="4" t="s">
+    <row r="59" spans="1:13">
+      <c r="A59" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" t="s">
+        <v>91</v>
+      </c>
+      <c r="I59" t="s">
+        <v>91</v>
+      </c>
+      <c r="M59">
         <v>58</v>
       </c>
-      <c r="C34" t="s">
-        <v>17</v>
-      </c>
-      <c r="I34" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" s="4" t="s">
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M60">
         <v>59</v>
       </c>
-      <c r="C35" t="s">
-        <v>17</v>
-      </c>
-      <c r="I35" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" ht="25.5" spans="1:9">
-      <c r="B36" s="4" t="s">
+    </row>
+    <row r="61" spans="1:13">
+      <c r="B61" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C61" t="s">
+        <v>39</v>
+      </c>
+      <c r="I61" t="s">
+        <v>39</v>
+      </c>
+      <c r="M61">
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" s="4" t="s">
+    <row r="62" spans="1:13">
+      <c r="A62" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M62">
         <v>61</v>
       </c>
-      <c r="C37" t="s">
-        <v>25</v>
-      </c>
-      <c r="I37" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" t="s">
-        <v>18</v>
-      </c>
-      <c r="B38" s="4" t="s">
+    </row>
+    <row r="63" ht="40.5" spans="1:13">
+      <c r="B63" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M63">
         <v>62</v>
       </c>
-      <c r="C38" s="7"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" s="1" t="s">
+    </row>
+    <row r="64" spans="1:13">
+      <c r="B64" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M64">
         <v>63</v>
       </c>
     </row>
-    <row r="40" ht="25.5" spans="1:9">
-      <c r="B40" s="6" t="s">
+    <row r="65" spans="1:15">
+      <c r="A65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M65">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
-      <c r="A41" t="s">
-        <v>18</v>
-      </c>
-      <c r="B41" s="1" t="s">
+    <row r="66" spans="1:15">
+      <c r="A66" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M66">
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" s="1" t="s">
+    <row r="67" spans="1:15">
+      <c r="B67" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M67">
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
-      <c r="A43" t="s">
-        <v>18</v>
-      </c>
-      <c r="B43" s="1" t="s">
+    <row r="68" ht="25.5" spans="1:15">
+      <c r="B68" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M68">
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="1" t="s">
+    <row r="69" spans="1:15">
+      <c r="A69" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M69">
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
-      <c r="A45" t="s">
-        <v>18</v>
-      </c>
-      <c r="B45" s="1" t="s">
+    <row r="70" spans="1:15">
+      <c r="B70" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M70">
         <v>69</v>
       </c>
     </row>
-    <row r="46" ht="27" spans="1:9">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" s="1" t="s">
+    <row r="71" spans="1:15">
+      <c r="A71" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M71">
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
-      <c r="A47" t="s">
-        <v>18</v>
-      </c>
-      <c r="B47" s="1" t="s">
+    <row r="72" spans="1:15">
+      <c r="B72" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M72">
         <v>71</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
-      <c r="B48" s="1" t="s">
+    <row r="73" spans="1:15">
+      <c r="A73" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M73">
         <v>72</v>
       </c>
     </row>
-    <row r="49" ht="27" spans="1:2">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="1" t="s">
+    <row r="74" spans="1:15">
+      <c r="B74" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M74">
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>18</v>
-      </c>
-      <c r="B50" s="1" t="s">
+    <row r="75" ht="27" spans="1:15">
+      <c r="A75" t="s">
+        <v>19</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C75" t="s">
+        <v>108</v>
+      </c>
+      <c r="I75" t="s">
+        <v>108</v>
+      </c>
+      <c r="M75">
         <v>74</v>
       </c>
-    </row>
-    <row r="51" ht="27" spans="1:2">
-      <c r="B51" s="1" t="s">
+      <c r="O75" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="B76" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="M76">
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" s="1" t="s">
+    <row r="77" spans="1:15">
+      <c r="A77" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M77">
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
-      <c r="B53" s="6" t="s">
+    <row r="78" spans="1:15">
+      <c r="A78" t="s">
+        <v>19</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C78" t="s">
+        <v>108</v>
+      </c>
+      <c r="I78" t="s">
+        <v>108</v>
+      </c>
+      <c r="M78">
         <v>77</v>
       </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" s="1" t="s">
+      <c r="O78" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="79" ht="25.5" spans="1:15">
+      <c r="B79" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="M79">
         <v>78</v>
       </c>
     </row>
-    <row r="55" ht="27" spans="1:2">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" s="1" t="s">
+    <row r="80" spans="1:15">
+      <c r="A80" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M80">
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
-      <c r="B56" s="6" t="s">
+    <row r="81" spans="1:13">
+      <c r="B81" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="M81">
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>18</v>
-      </c>
-      <c r="B57" s="1" t="s">
+    <row r="82" spans="1:13">
+      <c r="A82" t="s">
+        <v>19</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C82" t="s">
+        <v>52</v>
+      </c>
+      <c r="I82" t="s">
+        <v>52</v>
+      </c>
+      <c r="M82">
         <v>81</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" s="1" t="s">
+    <row r="83" spans="1:13">
+      <c r="A83" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="M83">
         <v>82</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>18</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="61" ht="27" spans="1:2">
-      <c r="B61" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="B62" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>18</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>18</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="B65" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="66" ht="25.5" spans="1:2">
-      <c r="B66" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>18</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="B68" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" t="s">
-        <v>18</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="B70" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" t="s">
-        <v>18</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="B72" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="B74" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" t="s">
-        <v>18</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="B77" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" t="s">
-        <v>18</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="B79" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
-      <c r="A81" t="s">
-        <v>18</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
-      <c r="A82" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8"/>
-    </row>
-    <row r="83" spans="1:9">
-      <c r="A83" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:13">
       <c r="A84" s="8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C84" s="8"/>
       <c r="D84" s="8"/>
@@ -2532,16 +2927,19 @@
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
       <c r="I84" s="8"/>
-    </row>
-    <row r="85" spans="1:9">
+      <c r="M84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13">
       <c r="A85" s="8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="D85" s="8"/>
       <c r="E85" s="8"/>
@@ -2549,52 +2947,61 @@
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
       <c r="I85" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
+        <v>39</v>
+      </c>
+      <c r="M85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13">
       <c r="A86" s="8" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>33</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C86" s="8"/>
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
-      <c r="I86" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
+      <c r="I86" s="8"/>
+      <c r="M86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13">
       <c r="A87" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C87" s="8"/>
+        <v>121</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="D87" s="8"/>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
-      <c r="I87" s="8"/>
-    </row>
-    <row r="88" spans="1:9">
+      <c r="I87" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="M87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13">
       <c r="A88" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D88" s="8"/>
       <c r="E88" s="8"/>
@@ -2602,15 +3009,18 @@
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
       <c r="I88" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9">
+        <v>36</v>
+      </c>
+      <c r="M88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13">
       <c r="A89" s="8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
@@ -2619,16 +3029,19 @@
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
       <c r="I89" s="8"/>
-    </row>
-    <row r="90" ht="54" spans="1:9">
+      <c r="M89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13">
       <c r="A90" s="8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D90" s="8"/>
       <c r="E90" s="8"/>
@@ -2636,13 +3049,18 @@
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
       <c r="I90" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9">
-      <c r="A91" s="8"/>
-      <c r="B91" s="4" t="s">
-        <v>116</v>
+        <v>39</v>
+      </c>
+      <c r="M90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="A91" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
@@ -2651,16 +3069,19 @@
       <c r="G91" s="8"/>
       <c r="H91" s="8"/>
       <c r="I91" s="8"/>
-    </row>
-    <row r="92" spans="1:9">
+      <c r="M91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" ht="27" spans="1:13">
       <c r="A92" s="8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="D92" s="8"/>
       <c r="E92" s="8"/>
@@ -2668,33 +3089,43 @@
       <c r="G92" s="8"/>
       <c r="H92" s="8"/>
       <c r="I92" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9">
+        <v>127</v>
+      </c>
+      <c r="M92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" ht="27" spans="1:13">
       <c r="A93" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C93" s="8"/>
+        <v>128</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="D93" s="8"/>
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
       <c r="H93" s="8"/>
-      <c r="I93" s="8"/>
-    </row>
-    <row r="94" spans="1:9">
+      <c r="I93" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" ht="27" spans="1:13">
       <c r="A94" s="8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D94" s="8"/>
       <c r="E94" s="8"/>
@@ -2702,26 +3133,38 @@
       <c r="G94" s="8"/>
       <c r="H94" s="8"/>
       <c r="I94" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="95" ht="25.5" spans="1:9">
-      <c r="A95" s="8"/>
-      <c r="B95" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C95" s="8"/>
+        <v>32</v>
+      </c>
+      <c r="M94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13">
+      <c r="A95" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="D95" s="8"/>
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
       <c r="H95" s="8"/>
-      <c r="I95" s="8"/>
-    </row>
-    <row r="96" ht="51" spans="1:9">
+      <c r="I95" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13">
       <c r="A96" s="8"/>
-      <c r="B96" s="6" t="s">
-        <v>121</v>
+      <c r="B96" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="C96" s="8"/>
       <c r="D96" s="8"/>
@@ -2730,60 +3173,76 @@
       <c r="G96" s="8"/>
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
-    </row>
-    <row r="97" spans="1:9">
+      <c r="M96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13">
       <c r="A97" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C97" s="8"/>
+        <v>132</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
-      <c r="I97" s="8"/>
-    </row>
-    <row r="98" ht="27" spans="1:9">
+      <c r="I97" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13">
       <c r="A98" s="8" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>46</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C98" s="8"/>
       <c r="D98" s="8"/>
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
-      <c r="I98" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="99" ht="38.25" spans="1:9">
-      <c r="A99" s="8"/>
-      <c r="B99" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C99" s="8"/>
+      <c r="I98" s="8"/>
+      <c r="M98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13">
+      <c r="A99" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="D99" s="8"/>
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
-      <c r="I99" s="8"/>
-    </row>
-    <row r="100" spans="1:9">
-      <c r="A100" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>125</v>
+      <c r="I99" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" ht="25.5" spans="1:13">
+      <c r="A100" s="8"/>
+      <c r="B100" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
@@ -2792,32 +3251,34 @@
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
-    </row>
-    <row r="101" spans="1:9">
-      <c r="A101" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>46</v>
-      </c>
+      <c r="M100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" ht="76.5" spans="1:13">
+      <c r="A101" s="8"/>
+      <c r="B101" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C101" s="8"/>
       <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
+      <c r="E101" s="8" t="s">
+        <v>137</v>
+      </c>
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
-      <c r="I101" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9">
+      <c r="I101" s="8"/>
+      <c r="M101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13">
       <c r="A102" s="8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
@@ -2826,16 +3287,19 @@
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
       <c r="I102" s="8"/>
-    </row>
-    <row r="103" spans="1:9">
+      <c r="M102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" ht="40.5" spans="1:13">
       <c r="A103" s="8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D103" s="8"/>
       <c r="E103" s="8"/>
@@ -2843,15 +3307,16 @@
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
       <c r="I103" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="104" ht="27" spans="1:9">
-      <c r="A104" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>129</v>
+        <v>52</v>
+      </c>
+      <c r="M103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" ht="51" spans="1:13">
+      <c r="A104" s="8"/>
+      <c r="B104" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="C104" s="8"/>
       <c r="D104" s="8"/>
@@ -2860,11 +3325,16 @@
       <c r="G104" s="8"/>
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
-    </row>
-    <row r="105" spans="1:9">
-      <c r="A105" s="8"/>
-      <c r="B105" s="4" t="s">
-        <v>130</v>
+      <c r="M104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13">
+      <c r="A105" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
@@ -2873,16 +3343,19 @@
       <c r="G105" s="8"/>
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
-    </row>
-    <row r="106" spans="1:9">
+      <c r="M105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13">
       <c r="A106" s="8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
@@ -2890,15 +3363,18 @@
       <c r="G106" s="8"/>
       <c r="H106" s="8"/>
       <c r="I106" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="107" ht="27" spans="1:9">
+        <v>52</v>
+      </c>
+      <c r="M106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" ht="27" spans="1:13">
       <c r="A107" s="8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C107" s="8"/>
       <c r="D107" s="8"/>
@@ -2907,16 +3383,19 @@
       <c r="G107" s="8"/>
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
-    </row>
-    <row r="108" spans="1:9">
+      <c r="M107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" ht="27" spans="1:13">
       <c r="A108" s="8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8"/>
@@ -2924,46 +3403,63 @@
       <c r="G108" s="8"/>
       <c r="H108" s="8"/>
       <c r="I108" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="109" ht="40.5" spans="1:9">
+        <v>39</v>
+      </c>
+      <c r="M108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13">
       <c r="A109" s="8" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C109" s="8"/>
+        <v>146</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>147</v>
+      </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
       <c r="H109" s="8"/>
       <c r="I109" s="8"/>
-    </row>
-    <row r="110" spans="1:9">
-      <c r="A110" s="8"/>
-      <c r="B110" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C110" s="8"/>
+      <c r="M109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13">
+      <c r="A110" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
       <c r="G110" s="8"/>
       <c r="H110" s="8"/>
-      <c r="I110" s="8"/>
-    </row>
-    <row r="111" spans="1:9">
+      <c r="I110" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13">
       <c r="A111" s="8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8"/>
@@ -2971,15 +3467,16 @@
       <c r="G111" s="8"/>
       <c r="H111" s="8"/>
       <c r="I111" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="112" ht="54" spans="1:9">
-      <c r="A112" s="8" t="s">
-        <v>18</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="M111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13">
+      <c r="A112" s="8"/>
       <c r="B112" s="1" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="C112" s="8"/>
       <c r="D112" s="8"/>
@@ -2988,32 +3485,32 @@
       <c r="G112" s="8"/>
       <c r="H112" s="8"/>
       <c r="I112" s="8"/>
-    </row>
-    <row r="113" spans="1:9">
+      <c r="M112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" ht="40.5" spans="1:15">
       <c r="A113" s="8" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>17</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="C113" s="8"/>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
       <c r="H113" s="8"/>
-      <c r="I113" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9">
-      <c r="A114" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>139</v>
+      <c r="I113" s="8"/>
+      <c r="M113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114" s="8"/>
+      <c r="B114" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="8"/>
@@ -3022,26 +3519,38 @@
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
       <c r="I114" s="8"/>
-    </row>
-    <row r="115" spans="1:9">
-      <c r="A115" s="8"/>
-      <c r="B115" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C115" s="8"/>
+      <c r="M114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>52</v>
+      </c>
       <c r="D115" s="8"/>
-      <c r="E115" s="8" t="s">
-        <v>40</v>
-      </c>
+      <c r="E115" s="8"/>
       <c r="F115" s="8"/>
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
-      <c r="I115" s="8"/>
-    </row>
-    <row r="116" ht="25.5" spans="1:9">
-      <c r="A116" s="8"/>
-      <c r="B116" s="6" t="s">
-        <v>141</v>
+      <c r="I115" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" ht="40.5" spans="1:15">
+      <c r="A116" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="8"/>
@@ -3050,26 +3559,39 @@
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
       <c r="I116" s="8"/>
-    </row>
-    <row r="117" spans="1:9">
-      <c r="A117" s="8"/>
-      <c r="B117" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C117" s="8"/>
+      <c r="M116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
-      <c r="F117" s="8" t="s">
-        <v>143</v>
-      </c>
+      <c r="F117" s="8"/>
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
-      <c r="I117" s="8"/>
-    </row>
-    <row r="118" spans="1:9">
+      <c r="I117" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M117">
+        <v>116</v>
+      </c>
+      <c r="O117" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
       <c r="A118" s="8"/>
-      <c r="B118" s="6" t="s">
-        <v>113</v>
+      <c r="B118" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
@@ -3078,11 +3600,16 @@
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
       <c r="I118" s="8"/>
-    </row>
-    <row r="119" spans="1:9">
-      <c r="A119" s="8"/>
-      <c r="B119" s="6" t="s">
-        <v>142</v>
+      <c r="M118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="C119" s="8"/>
       <c r="D119" s="8"/>
@@ -3091,26 +3618,38 @@
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
       <c r="I119" s="8"/>
-    </row>
-    <row r="120" spans="1:9">
-      <c r="A120" s="8"/>
-      <c r="B120" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C120" s="8"/>
+      <c r="M119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="D120" s="8"/>
-      <c r="E120" s="8" t="s">
-        <v>145</v>
-      </c>
+      <c r="E120" s="8"/>
       <c r="F120" s="8"/>
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
-      <c r="I120" s="8"/>
-    </row>
-    <row r="121" spans="1:9">
-      <c r="A121" s="8"/>
-      <c r="B121" s="6" t="s">
-        <v>146</v>
+      <c r="I120" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="C121" s="8"/>
       <c r="D121" s="8"/>
@@ -3119,11 +3658,16 @@
       <c r="G121" s="8"/>
       <c r="H121" s="8"/>
       <c r="I121" s="8"/>
-    </row>
-    <row r="122" ht="27" spans="1:9">
-      <c r="A122" s="8"/>
-      <c r="B122" s="6" t="s">
-        <v>147</v>
+      <c r="M121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15">
+      <c r="A122" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="C122" s="8"/>
       <c r="D122" s="8"/>
@@ -3132,11 +3676,14 @@
       <c r="G122" s="8"/>
       <c r="H122" s="8"/>
       <c r="I122" s="8"/>
-    </row>
-    <row r="123" ht="26.25" spans="1:9">
+      <c r="M122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15">
       <c r="A123" s="8"/>
       <c r="B123" s="4" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="8"/>
@@ -3145,24 +3692,38 @@
       <c r="G123" s="8"/>
       <c r="H123" s="8"/>
       <c r="I123" s="8"/>
-    </row>
-    <row r="124" ht="25.5" spans="1:9">
-      <c r="A124" s="8"/>
-      <c r="B124" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C124" s="8"/>
+      <c r="M123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15">
+      <c r="A124" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8"/>
       <c r="F124" s="8"/>
       <c r="G124" s="8"/>
       <c r="H124" s="8"/>
-      <c r="I124" s="8"/>
-    </row>
-    <row r="125" spans="1:9">
-      <c r="A125" s="8"/>
-      <c r="B125" s="6" t="s">
-        <v>150</v>
+      <c r="I124" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" ht="27" spans="1:15">
+      <c r="A125" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="C125" s="8"/>
       <c r="D125" s="8"/>
@@ -3171,24 +3732,38 @@
       <c r="G125" s="8"/>
       <c r="H125" s="8"/>
       <c r="I125" s="8"/>
-    </row>
-    <row r="126" ht="25.5" spans="1:9">
-      <c r="A126" s="8"/>
-      <c r="B126" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C126" s="8"/>
+      <c r="M125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15">
+      <c r="A126" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
       <c r="G126" s="8"/>
       <c r="H126" s="8"/>
-      <c r="I126" s="8"/>
-    </row>
-    <row r="127" spans="1:9">
-      <c r="A127" s="8"/>
-      <c r="B127" s="6" t="s">
-        <v>152</v>
+      <c r="I126" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15">
+      <c r="A127" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C127" s="8"/>
       <c r="D127" s="8"/>
@@ -3197,13 +3772,16 @@
       <c r="G127" s="8"/>
       <c r="H127" s="8"/>
       <c r="I127" s="8"/>
-    </row>
-    <row r="128" spans="1:9">
+      <c r="M127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15">
       <c r="A128" s="8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C128" s="8"/>
       <c r="D128" s="8"/>
@@ -3212,24 +3790,38 @@
       <c r="G128" s="8"/>
       <c r="H128" s="8"/>
       <c r="I128" s="8"/>
-    </row>
-    <row r="129" spans="1:9">
-      <c r="A129" s="8"/>
-      <c r="B129" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C129" s="8"/>
+      <c r="M128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13">
+      <c r="A129" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
       <c r="G129" s="8"/>
       <c r="H129" s="8"/>
-      <c r="I129" s="8"/>
-    </row>
-    <row r="130" spans="1:9">
-      <c r="A130" s="8"/>
+      <c r="I129" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" ht="40.5" spans="1:13">
+      <c r="A130" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="B130" s="1" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="C130" s="8"/>
       <c r="D130" s="8"/>
@@ -3238,11 +3830,16 @@
       <c r="G130" s="8"/>
       <c r="H130" s="8"/>
       <c r="I130" s="8"/>
-    </row>
-    <row r="131" spans="1:9">
-      <c r="A131" s="8"/>
+      <c r="M130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" ht="27" spans="1:13">
+      <c r="A131" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="B131" s="1" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="C131" s="8"/>
       <c r="D131" s="8"/>
@@ -3251,26 +3848,38 @@
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
       <c r="I131" s="8"/>
-    </row>
-    <row r="132" spans="1:9">
-      <c r="A132" s="8"/>
+      <c r="M131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13">
+      <c r="A132" s="8" t="s">
+        <v>19</v>
+      </c>
       <c r="B132" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C132" s="8"/>
+        <v>169</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="D132" s="8"/>
-      <c r="E132" s="8" t="s">
-        <v>156</v>
-      </c>
+      <c r="E132" s="8"/>
       <c r="F132" s="8"/>
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
-      <c r="I132" s="8"/>
-    </row>
-    <row r="133" spans="1:9">
-      <c r="A133" s="8"/>
+      <c r="I132" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" ht="27" spans="1:13">
+      <c r="A133" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="B133" s="1" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="C133" s="8"/>
       <c r="D133" s="8"/>
@@ -3279,11 +3888,16 @@
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
       <c r="I133" s="8"/>
-    </row>
-    <row r="134" spans="1:9">
-      <c r="A134" s="8"/>
+      <c r="M133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" ht="27" spans="1:13">
+      <c r="A134" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="B134" s="1" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
       <c r="C134" s="8"/>
       <c r="D134" s="8"/>
@@ -3292,21 +3906,399 @@
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
       <c r="I134" s="8"/>
-    </row>
-    <row r="135" spans="1:9">
+      <c r="M134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13">
       <c r="A135" s="8" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C135" s="8"/>
+        <v>172</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
-      <c r="I135" s="8"/>
+      <c r="I135" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13">
+      <c r="A136" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C136" s="8"/>
+      <c r="D136" s="8"/>
+      <c r="E136" s="8"/>
+      <c r="F136" s="8"/>
+      <c r="G136" s="8"/>
+      <c r="H136" s="8"/>
+      <c r="I136" s="8"/>
+      <c r="M136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13">
+      <c r="A137" s="8"/>
+      <c r="B137" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C137" s="8"/>
+      <c r="D137" s="8"/>
+      <c r="E137" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F137" s="8"/>
+      <c r="G137" s="8"/>
+      <c r="H137" s="8"/>
+      <c r="I137" s="8"/>
+      <c r="M137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" ht="51" spans="1:13">
+      <c r="A138" s="8"/>
+      <c r="B138" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C138" s="8"/>
+      <c r="D138" s="8"/>
+      <c r="E138" s="8"/>
+      <c r="F138" s="8"/>
+      <c r="G138" s="8"/>
+      <c r="H138" s="8"/>
+      <c r="I138" s="8"/>
+      <c r="M138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13">
+      <c r="A139" s="8"/>
+      <c r="B139" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C139" s="8"/>
+      <c r="D139" s="8"/>
+      <c r="E139" s="8"/>
+      <c r="F139" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G139" s="8"/>
+      <c r="H139" s="8"/>
+      <c r="I139" s="8"/>
+      <c r="M139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13">
+      <c r="A140" s="8"/>
+      <c r="B140" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C140" s="8"/>
+      <c r="D140" s="8"/>
+      <c r="E140" s="8"/>
+      <c r="F140" s="8"/>
+      <c r="G140" s="8"/>
+      <c r="H140" s="8"/>
+      <c r="I140" s="8"/>
+      <c r="M140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13">
+      <c r="A141" s="8"/>
+      <c r="B141" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C141" s="8"/>
+      <c r="D141" s="8"/>
+      <c r="E141" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F141" s="8"/>
+      <c r="G141" s="8"/>
+      <c r="H141" s="8"/>
+      <c r="I141" s="8"/>
+      <c r="M141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13">
+      <c r="A142" s="8"/>
+      <c r="B142" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C142" s="8"/>
+      <c r="D142" s="8"/>
+      <c r="E142" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F142" s="8"/>
+      <c r="G142" s="8"/>
+      <c r="H142" s="8"/>
+      <c r="I142" s="8"/>
+      <c r="M142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13">
+      <c r="A143" s="8"/>
+      <c r="B143" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C143" s="8"/>
+      <c r="D143" s="8"/>
+      <c r="E143" s="8"/>
+      <c r="F143" s="8"/>
+      <c r="G143" s="8"/>
+      <c r="H143" s="8"/>
+      <c r="I143" s="8"/>
+      <c r="M143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" ht="27" spans="1:13">
+      <c r="A144" s="8"/>
+      <c r="B144" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C144" s="8"/>
+      <c r="D144" s="8"/>
+      <c r="E144" s="8"/>
+      <c r="F144" s="8"/>
+      <c r="G144" s="8"/>
+      <c r="H144" s="8"/>
+      <c r="I144" s="8"/>
+      <c r="M144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" ht="51.75" spans="1:13">
+      <c r="A145" s="8"/>
+      <c r="B145" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C145" s="8"/>
+      <c r="D145" s="8"/>
+      <c r="E145" s="8"/>
+      <c r="F145" s="8"/>
+      <c r="G145" s="8"/>
+      <c r="H145" s="8"/>
+      <c r="I145" s="8"/>
+      <c r="M145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" ht="38.25" spans="1:13">
+      <c r="A146" s="8"/>
+      <c r="B146" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C146" s="8"/>
+      <c r="D146" s="8"/>
+      <c r="E146" s="8"/>
+      <c r="F146" s="8"/>
+      <c r="G146" s="8"/>
+      <c r="H146" s="8"/>
+      <c r="I146" s="8"/>
+      <c r="M146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13">
+      <c r="A147" s="8"/>
+      <c r="B147" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C147" s="8"/>
+      <c r="D147" s="8"/>
+      <c r="E147" s="8"/>
+      <c r="F147" s="8"/>
+      <c r="G147" s="8"/>
+      <c r="H147" s="8"/>
+      <c r="I147" s="8"/>
+      <c r="M147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" ht="25.5" spans="1:13">
+      <c r="A148" s="8"/>
+      <c r="B148" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C148" s="8"/>
+      <c r="D148" s="8"/>
+      <c r="E148" s="8"/>
+      <c r="F148" s="8"/>
+      <c r="G148" s="8"/>
+      <c r="H148" s="8"/>
+      <c r="I148" s="8"/>
+      <c r="M148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13">
+      <c r="A149" s="8"/>
+      <c r="B149" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C149" s="8"/>
+      <c r="D149" s="8"/>
+      <c r="E149" s="8"/>
+      <c r="F149" s="8"/>
+      <c r="G149" s="8"/>
+      <c r="H149" s="8"/>
+      <c r="I149" s="8"/>
+      <c r="M149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13">
+      <c r="A150" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C150" s="8"/>
+      <c r="D150" s="8"/>
+      <c r="E150" s="8"/>
+      <c r="F150" s="8"/>
+      <c r="G150" s="8"/>
+      <c r="H150" s="8"/>
+      <c r="I150" s="8"/>
+      <c r="M150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" ht="25.5" spans="1:13">
+      <c r="A151" s="8"/>
+      <c r="B151" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C151" s="8"/>
+      <c r="D151" s="8"/>
+      <c r="E151" s="8"/>
+      <c r="F151" s="8"/>
+      <c r="G151" s="8"/>
+      <c r="H151" s="8"/>
+      <c r="I151" s="8"/>
+      <c r="M151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13">
+      <c r="A152" s="8"/>
+      <c r="B152" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C152" s="8"/>
+      <c r="D152" s="8"/>
+      <c r="E152" s="8"/>
+      <c r="F152" s="8"/>
+      <c r="G152" s="8"/>
+      <c r="H152" s="8"/>
+      <c r="I152" s="8"/>
+      <c r="M152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13">
+      <c r="A153" s="8"/>
+      <c r="B153" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C153" s="8"/>
+      <c r="D153" s="8"/>
+      <c r="E153" s="8"/>
+      <c r="F153" s="8"/>
+      <c r="G153" s="8"/>
+      <c r="H153" s="8"/>
+      <c r="I153" s="8"/>
+      <c r="M153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13">
+      <c r="A154" s="8"/>
+      <c r="B154" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C154" s="8"/>
+      <c r="D154" s="8"/>
+      <c r="E154" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="F154" s="8"/>
+      <c r="G154" s="8"/>
+      <c r="H154" s="8"/>
+      <c r="I154" s="8"/>
+      <c r="M154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13">
+      <c r="A155" s="8"/>
+      <c r="B155" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C155" s="8"/>
+      <c r="D155" s="8"/>
+      <c r="E155" s="8"/>
+      <c r="F155" s="8"/>
+      <c r="G155" s="8"/>
+      <c r="H155" s="8"/>
+      <c r="I155" s="8"/>
+      <c r="M155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13">
+      <c r="A156" s="8"/>
+      <c r="B156" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C156" s="8"/>
+      <c r="D156" s="8"/>
+      <c r="E156" s="8"/>
+      <c r="F156" s="8"/>
+      <c r="G156" s="8"/>
+      <c r="H156" s="8"/>
+      <c r="I156" s="8"/>
+      <c r="M156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13">
+      <c r="A157" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C157" s="8"/>
+      <c r="D157" s="8"/>
+      <c r="E157" s="8"/>
+      <c r="F157" s="8"/>
+      <c r="G157" s="8"/>
+      <c r="H157" s="8"/>
+      <c r="I157" s="8"/>
+      <c r="M157">
+        <v>156</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
